--- a/artfynd/A 45078-2025 artfynd.xlsx
+++ b/artfynd/A 45078-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>102804603</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607692.6185447269</v>
+        <v>607692</v>
       </c>
       <c r="R2" t="n">
-        <v>7046168.265609819</v>
+        <v>7046168</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118121125</v>
+        <v>118121124</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607682</v>
+        <v>607931</v>
       </c>
       <c r="R3" t="n">
-        <v>7046042</v>
+        <v>7045925</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,37 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118121122</v>
+        <v>118121136</v>
       </c>
       <c r="B4" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607931</v>
+        <v>607978</v>
       </c>
       <c r="R4" t="n">
-        <v>7045825</v>
+        <v>7045911</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,37 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118121124</v>
+        <v>118121125</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607931</v>
+        <v>607682</v>
       </c>
       <c r="R5" t="n">
-        <v>7045925</v>
+        <v>7046042</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118121134</v>
+        <v>118121127</v>
       </c>
       <c r="B6" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607978</v>
+        <v>607630</v>
       </c>
       <c r="R6" t="n">
-        <v>7045911</v>
+        <v>7046066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,37 +1161,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118121138</v>
+        <v>118121134</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118121127</v>
+        <v>118121122</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607630</v>
+        <v>607931</v>
       </c>
       <c r="R8" t="n">
-        <v>7046066</v>
+        <v>7045825</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,37 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118121133</v>
+        <v>118121138</v>
       </c>
       <c r="B9" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,13 +1390,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607630</v>
+        <v>607978</v>
       </c>
       <c r="R9" t="n">
-        <v>7046066</v>
+        <v>7045911</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,15 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118121136</v>
+        <v>118121133</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,13 +1487,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607978</v>
+        <v>607630</v>
       </c>
       <c r="R10" t="n">
-        <v>7045911</v>
+        <v>7046066</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 45078-2025 artfynd.xlsx
+++ b/artfynd/A 45078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102804603</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121124</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121136</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121127</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121134</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121122</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121138</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,8 +1591,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121133</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>